--- a/excel_files/progress.xlsx
+++ b/excel_files/progress.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8025EF90-7B3A-4771-B5F9-028EFC264771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A80FB4-684D-46AD-AE31-02461B35850D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Exceptions &amp; Logging" sheetId="1" r:id="rId1"/>
+    <sheet name="AudioArt" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>module.py</t>
   </si>
@@ -87,15 +88,6 @@
     <t>test_audio_art.py</t>
   </si>
   <si>
-    <t>test_audio_playlist.py</t>
-  </si>
-  <si>
-    <t>test_directory_processing.py</t>
-  </si>
-  <si>
-    <t>test_audio_normalization.py</t>
-  </si>
-  <si>
     <t>exceptions</t>
   </si>
   <si>
@@ -108,14 +100,59 @@
     <t>YES</t>
   </si>
   <si>
-    <t>NO</t>
+    <t>__init__</t>
+  </si>
+  <si>
+    <t>__unpack_asf_image</t>
+  </si>
+  <si>
+    <t>__write_data</t>
+  </si>
+  <si>
+    <t>extract_album_art</t>
+  </si>
+  <si>
+    <t>extract_asf_art</t>
+  </si>
+  <si>
+    <t>extract_ffmpeg_art</t>
+  </si>
+  <si>
+    <t>extract_m4a_art</t>
+  </si>
+  <si>
+    <t>extract_mp3_art</t>
+  </si>
+  <si>
+    <t>has_video_stream</t>
+  </si>
+  <si>
+    <t>set_album_art</t>
+  </si>
+  <si>
+    <t>extract_walk</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>AudioArt</t>
+  </si>
+  <si>
+    <t>Instance defs</t>
+  </si>
+  <si>
+    <t>TestAudioArt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,6 +167,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -146,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -170,43 +212,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -382,7 +387,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -395,7 +402,9 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -408,35 +417,40 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -751,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52C8D77-F5C1-45CD-953A-8D7692FB0F27}">
-  <dimension ref="B1:F17"/>
+  <dimension ref="B1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -759,10 +773,9 @@
     <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,204 +783,254 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="3"/>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E4" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="3"/>
+      <c r="C6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="3"/>
+      <c r="C7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="4"/>
+      <c r="C8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="4"/>
+      <c r="C12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AE1BA9-3CF4-42ED-A40E-49B961F28E01}">
+  <dimension ref="B1:D14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="10" t="s">
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="6"/>
-      <c r="C3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="7"/>
-      <c r="C4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="15" t="s">
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="16" t="s">
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="6"/>
-      <c r="C6" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="7"/>
-      <c r="C8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="16"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="7"/>
-      <c r="C10" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="7"/>
-      <c r="C12" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="16"/>
-    </row>
-    <row r="13" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="4"/>
-      <c r="C17" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="16"/>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel_files/progress.xlsx
+++ b/excel_files/progress.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A80FB4-684D-46AD-AE31-02461B35850D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7D3273-4956-4FFA-B3DE-2FAB5D3EB23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
+    <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Exceptions &amp; Logging" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
   <si>
     <t>module.py</t>
   </si>
@@ -146,13 +146,189 @@
   </si>
   <si>
     <t>TestAudioArt</t>
+  </si>
+  <si>
+    <t>header updated</t>
+  </si>
+  <si>
+    <t>Exception prototcol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">except &lt;ExceptionNameError&gt; as en_error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">except &lt;ExceptionNameExxeption&gt; as en_exc </t>
+  </si>
+  <si>
+    <t>eg: except PathInfoError as pi_error:</t>
+  </si>
+  <si>
+    <t>eg: except Exception as e_error:</t>
+  </si>
+  <si>
+    <t>all excpetions get raised</t>
+  </si>
+  <si>
+    <t>eg: raise pi_error</t>
+  </si>
+  <si>
+    <t>eg: raise e_error</t>
+  </si>
+  <si>
+    <t>logger.exception ALWAYS gets stack_info=True</t>
+  </si>
+  <si>
+    <t>logger.error ALWAYS gets exc_info=True</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">if an exception is raised </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>outside</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of except block, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>log and raise it</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>excexpt block just re-raises</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">otherwise, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inside</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the except block,</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> log the error/exception</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> then raise it</t>
+    </r>
+  </si>
+  <si>
+    <t>format for generic handling block:</t>
+  </si>
+  <si>
+    <t>format for specific handling block:</t>
+  </si>
+  <si>
+    <t>        except MutagenError as m_error:</t>
+  </si>
+  <si>
+    <t>            logger.error(f"MutagenError {m_error} loading {file_path}", exc_info=True)</t>
+  </si>
+  <si>
+    <t>            raise m_error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    except Exception as e_error:</t>
+  </si>
+  <si>
+    <t>        logger.exception(f"Exception {type(e_error).__name__}  &lt;appropriate message here&gt;", stack_info=True)</t>
+  </si>
+  <si>
+    <t>        raise e_error</t>
+  </si>
+  <si>
+    <t>logger.info and logger.warning get neither</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +349,32 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -188,27 +390,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -226,231 +413,31 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -765,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52C8D77-F5C1-45CD-953A-8D7692FB0F27}">
-  <dimension ref="B1:E13"/>
+  <dimension ref="B1:S24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -773,157 +760,313 @@
     <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="9" max="19" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="F1" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="9" t="s">
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
-      <c r="C6" s="9" t="s">
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="9" t="s">
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="I6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="N7" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="I10" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="14" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="I12" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>19</v>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="I13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="I16" s="8"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I19" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I20" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I22" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I23" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I24" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -978,12 +1121,12 @@
       <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
     </row>

--- a/excel_files/progress.xlsx
+++ b/excel_files/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7D3273-4956-4FFA-B3DE-2FAB5D3EB23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F0FE36-D316-4957-83A9-81D141387FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="59">
   <si>
     <t>module.py</t>
   </si>
@@ -328,7 +328,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,13 +348,6 @@
       <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
@@ -417,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -425,19 +418,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -752,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B52C8D77-F5C1-45CD-953A-8D7692FB0F27}">
-  <dimension ref="B1:S24"/>
+  <dimension ref="B1:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -761,7 +753,6 @@
     <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" customWidth="1"/>
-    <col min="9" max="19" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -782,7 +773,7 @@
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -797,12 +788,12 @@
       <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="4"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
@@ -815,15 +806,15 @@
       <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="4"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
@@ -836,15 +827,15 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -861,7 +852,7 @@
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="4"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
@@ -872,15 +863,15 @@
         <v>20</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="I6" s="6" t="s">
+      <c r="I6" t="s">
         <v>43</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="4"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
@@ -891,12 +882,12 @@
         <v>20</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="N7" s="6" t="s">
+      <c r="N7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="4"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
@@ -909,7 +900,7 @@
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -924,12 +915,12 @@
       <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
@@ -940,12 +931,12 @@
         <v>20</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="I10" s="6" t="s">
+      <c r="I10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -962,19 +953,23 @@
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="F12" s="1"/>
-      <c r="I12" s="6" t="s">
+      <c r="I12" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -987,76 +982,76 @@
         <v>19</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="I16" s="8"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
     </row>
     <row r="17" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
     </row>
     <row r="18" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
     </row>
     <row r="19" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="20" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="21" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I21" s="7"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I23" s="6" t="s">
+      <c r="I23" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="24" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="6" t="s">
         <v>58</v>
       </c>
     </row>

--- a/excel_files/progress.xlsx
+++ b/excel_files/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F0FE36-D316-4957-83A9-81D141387FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FE2183-B8EA-4D17-BE6A-6EEC296D91BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
   <si>
     <t>module.py</t>
   </si>
@@ -862,7 +862,9 @@
       <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I6" t="s">
         <v>43</v>
       </c>
@@ -881,7 +883,9 @@
       <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="N7" t="s">
         <v>45</v>
       </c>
@@ -897,7 +901,9 @@
       <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -930,7 +936,9 @@
       <c r="E10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I10" t="s">
         <v>49</v>
       </c>
@@ -963,7 +971,9 @@
       <c r="E12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I12" t="s">
         <v>50</v>
       </c>
@@ -981,7 +991,9 @@
       <c r="E13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I13" s="6" t="s">
         <v>55</v>
       </c>

--- a/excel_files/progress.xlsx
+++ b/excel_files/progress.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MusicProcessing\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FE2183-B8EA-4D17-BE6A-6EEC296D91BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D853E31-C612-4B8D-B993-9E5CEEB0AE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-8232" yWindow="-13068" windowWidth="23256" windowHeight="12576" xr2:uid="{D1BCA01E-EFE2-441C-AE68-802A69D25AC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Exceptions &amp; Logging" sheetId="1" r:id="rId1"/>
-    <sheet name="AudioArt" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
   <si>
     <t>module.py</t>
   </si>
@@ -82,12 +81,6 @@
     <t>directory_processing.py</t>
   </si>
   <si>
-    <t>tests</t>
-  </si>
-  <si>
-    <t>test_audio_art.py</t>
-  </si>
-  <si>
     <t>exceptions</t>
   </si>
   <si>
@@ -98,54 +91,6 @@
   </si>
   <si>
     <t>YES</t>
-  </si>
-  <si>
-    <t>__init__</t>
-  </si>
-  <si>
-    <t>__unpack_asf_image</t>
-  </si>
-  <si>
-    <t>__write_data</t>
-  </si>
-  <si>
-    <t>extract_album_art</t>
-  </si>
-  <si>
-    <t>extract_asf_art</t>
-  </si>
-  <si>
-    <t>extract_ffmpeg_art</t>
-  </si>
-  <si>
-    <t>extract_m4a_art</t>
-  </si>
-  <si>
-    <t>extract_mp3_art</t>
-  </si>
-  <si>
-    <t>has_video_stream</t>
-  </si>
-  <si>
-    <t>set_album_art</t>
-  </si>
-  <si>
-    <t>extract_walk</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>AudioArt</t>
-  </si>
-  <si>
-    <t>Instance defs</t>
-  </si>
-  <si>
-    <t>TestAudioArt</t>
   </si>
   <si>
     <t>header updated</t>
@@ -328,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,11 +288,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <i/>
@@ -410,23 +350,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -756,315 +693,315 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>37</v>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="8"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="8"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="8"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="8"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="8"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="I14" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="I14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="I15" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="I15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="I16" s="6"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
     </row>
     <row r="17" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="I17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
     </row>
     <row r="18" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="I18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
     </row>
     <row r="19" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I19" s="5" t="s">
-        <v>53</v>
+      <c r="I19" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I20" s="5" t="s">
-        <v>54</v>
+      <c r="I20" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I21" s="5"/>
+      <c r="I21" s="4"/>
     </row>
     <row r="22" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I22" s="6" t="s">
-        <v>47</v>
+      <c r="I22" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I23" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="9:12" x14ac:dyDescent="0.25">
-      <c r="I24" s="6" t="s">
-        <v>58</v>
+      <c r="I24" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1076,113 +1013,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0AE1BA9-3CF4-42ED-A40E-49B961F28E01}">
-  <dimension ref="B1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>